--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -552,7 +552,7 @@
         <v>59.075</v>
       </c>
       <c r="I3" t="n">
-        <v>130.246020260492</v>
+        <v>131.2542068656047</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         <v>33.34</v>
       </c>
       <c r="I5" t="n">
-        <v>100.7681175553824</v>
+        <v>100</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -713,7 +713,7 @@
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>99.23188244461761</v>
+        <v>100</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>31.8</v>
       </c>
       <c r="I11" t="n">
-        <v>126.8173216074808</v>
+        <v>125.8506407423774</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>30.585</v>
       </c>
       <c r="I22" t="n">
-        <v>151.7310475342314</v>
+        <v>150.574458683164</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>28.26</v>
       </c>
       <c r="I34" t="n">
-        <v>57.53089168429255</v>
+        <v>57.09235528060097</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>49.11</v>
       </c>
       <c r="I51" t="n">
-        <v>63.69809640431927</v>
+        <v>63.21254971277066</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2719,7 +2719,7 @@
         <v>37.545</v>
       </c>
       <c r="I57" t="n">
-        <v>55.19314260269398</v>
+        <v>55.62037244783487</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3202,7 +3202,7 @@
         <v>59.83</v>
       </c>
       <c r="I69" t="n">
-        <v>158.4548591784482</v>
+        <v>159.6814000448732</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3242,7 +3242,7 @@
         <v>44.12</v>
       </c>
       <c r="I70" t="n">
-        <v>68.57397306022487</v>
+        <v>69.1047789993269</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44.31</v>
       </c>
       <c r="I71" t="n">
-        <v>40.40966269620394</v>
+        <v>40.10163499779054</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3442,7 +3442,7 @@
         <v>50.86</v>
       </c>
       <c r="I75" t="n">
-        <v>143.3596793944117</v>
+        <v>144.469374018398</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>50.5</v>
       </c>
       <c r="I77" t="n">
-        <v>129.8897918290104</v>
+        <v>128.8996906760937</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3885,7 +3885,7 @@
         <v>23.51</v>
       </c>
       <c r="I86" t="n">
-        <v>32.28320160302795</v>
+        <v>32.53309400942338</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
